--- a/test_data/api_cases.xlsx
+++ b/test_data/api_cases.xlsx
@@ -27,11 +27,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>case_name</t>
   </si>
   <si>
+    <t>module</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>method</t>
   </si>
   <si>
@@ -62,6 +68,12 @@
     <t>登录成功</t>
   </si>
   <si>
+    <t>用户模块</t>
+  </si>
+  <si>
+    <t>critical</t>
+  </si>
+  <si>
     <t>POST</t>
   </si>
   <si>
@@ -74,13 +86,7 @@
     <t>{"tel":"18218410011","captcha":"8888","type":1}</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>登录失败，验证码错误</t>
-  </si>
-  <si>
-    <t>{"tel":"18218410011","captcha":"8881","type":1}</t>
+    <t>msg</t>
   </si>
 </sst>
 </file>
@@ -93,8 +99,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -450,12 +462,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -564,16 +591,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -582,115 +606,118 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -698,9 +725,17 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1022,104 +1057,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelRow="2"/>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="24.5714285714286" customWidth="1"/>
-    <col min="2" max="2" width="8.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="17.8571428571429" customWidth="1"/>
     <col min="3" max="3" width="24.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="4" max="4" width="9.85714285714286" customWidth="1"/>
     <col min="5" max="5" width="48.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="13.1428571428571" customWidth="1"/>
-    <col min="7" max="7" width="11.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="13.8571428571429" customWidth="1"/>
-    <col min="9" max="9" width="38.5714285714286" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11.847619047619" customWidth="1"/>
+    <col min="8" max="8" width="13.847619047619" customWidth="1"/>
+    <col min="9" max="9" width="15.847619047619" customWidth="1"/>
+    <col min="10" max="10" width="13.847619047619" customWidth="1"/>
+    <col min="11" max="11" width="18.2761904761905" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1" customHeight="1" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" customHeight="1" spans="1:12">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2">
         <v>200</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>200</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1">
-        <v>-1</v>
-      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
